--- a/data/Posiciones.xlsx
+++ b/data/Posiciones.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30501"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\ADARVE JUV D.H\App_Rendimiento_Futbol\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="31" documentId="13_ncr:1_{ACE6BB03-6350-4C05-B9B8-BD6413AAC410}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6536530B-2EA3-42E4-9D38-2F86C06230EF}"/>
+  <xr:revisionPtr revIDLastSave="32" documentId="13_ncr:1_{ACE6BB03-6350-4C05-B9B8-BD6413AAC410}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5C2DD271-7B09-4739-8226-B05343D3D1A5}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{B961EC1D-9D64-4A12-AB9D-930ACB18AE51}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="99">
   <si>
     <t>Jugador</t>
   </si>
@@ -61,9 +61,6 @@
     <t>Delantero</t>
   </si>
   <si>
-    <t>Alejandro_Garcia_Gumiel</t>
-  </si>
-  <si>
     <t>Defensa Central</t>
   </si>
   <si>
@@ -172,9 +169,6 @@
     <t>48761553N</t>
   </si>
   <si>
-    <t>49592528C</t>
-  </si>
-  <si>
     <t>51522418A</t>
   </si>
   <si>
@@ -239,9 +233,6 @@
   </si>
   <si>
     <t>https://static.wixstatic.com/media/8ca434_3588209afd86455b901323c1cc6b9ae5~mv2.jpeg</t>
-  </si>
-  <si>
-    <t>https://static.wixstatic.com/media/8ca434_53cafa564de9472e8b20d0c9b47b3497~mv2.jpeg</t>
   </si>
   <si>
     <t>https://static.wixstatic.com/media/8ca434_230a74f2050a445681801cb0bc833646~mv2.jpeg</t>
@@ -1063,8 +1054,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{97812EF7-7207-445A-B780-D6046FF4E4C8}" name="Tabla1" displayName="Tabla1" ref="A1:G29" totalsRowShown="0">
-  <autoFilter ref="A1:G29" xr:uid="{97812EF7-7207-445A-B780-D6046FF4E4C8}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{97812EF7-7207-445A-B780-D6046FF4E4C8}" name="Tabla1" displayName="Tabla1" ref="A1:G28" totalsRowShown="0">
+  <autoFilter ref="A1:G28" xr:uid="{97812EF7-7207-445A-B780-D6046FF4E4C8}"/>
   <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{9890C0E8-1734-48AB-B9B8-F71F9B0FD391}" name="Jugador"/>
     <tableColumn id="2" xr3:uid="{F74319A2-3299-4382-8CC7-D4EC8D8793AD}" name="Posicion"/>
@@ -1375,7 +1366,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{86862050-FDEA-4FB1-B5DB-6F278968DFB2}">
-  <dimension ref="A1:G29"/>
+  <dimension ref="A1:G28"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="28.5546875" bestFit="1" customWidth="1"/>
@@ -1395,19 +1386,19 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G1" t="s">
         <v>43</v>
-      </c>
-      <c r="G1" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -1418,19 +1409,19 @@
         <v>3</v>
       </c>
       <c r="C2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D2" t="s">
+        <v>92</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>95</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>98</v>
       </c>
       <c r="F2" s="2">
         <v>39786</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -1441,19 +1432,19 @@
         <v>5</v>
       </c>
       <c r="C3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="F3" s="4">
         <v>39461</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -1464,19 +1455,19 @@
         <v>3</v>
       </c>
       <c r="C4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="F4" s="4">
         <v>39544</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -1487,19 +1478,19 @@
         <v>8</v>
       </c>
       <c r="C5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D5" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="F5" s="4">
         <v>39672</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -1510,19 +1501,19 @@
         <v>10</v>
       </c>
       <c r="C6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="F6" s="4">
         <v>39519</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -1533,42 +1524,42 @@
         <v>12</v>
       </c>
       <c r="C7" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D7" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F7" s="4">
         <v>39512</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C8" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="F8" s="4">
-        <v>39512</v>
+        <v>39507</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -1576,22 +1567,22 @@
         <v>15</v>
       </c>
       <c r="B9" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C9" t="s">
+        <v>35</v>
+      </c>
+      <c r="D9" t="s">
+        <v>50</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="F9" s="4">
+        <v>39866</v>
+      </c>
+      <c r="G9" s="5" t="s">
         <v>38</v>
-      </c>
-      <c r="D9" t="s">
-        <v>51</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="F9" s="4">
-        <v>39507</v>
-      </c>
-      <c r="G9" s="5" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -1599,22 +1590,22 @@
         <v>16</v>
       </c>
       <c r="B10" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C10" t="s">
         <v>36</v>
       </c>
       <c r="D10" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="F10" s="4">
-        <v>39866</v>
+        <v>39755</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -1622,22 +1613,22 @@
         <v>17</v>
       </c>
       <c r="B11" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="C11" t="s">
         <v>37</v>
       </c>
       <c r="D11" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="F11" s="4">
-        <v>39755</v>
+        <v>39492</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -1645,45 +1636,43 @@
         <v>18</v>
       </c>
       <c r="B12" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="C12" t="s">
+        <v>36</v>
+      </c>
+      <c r="D12" t="s">
+        <v>55</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="F12" s="4">
+        <v>39724</v>
+      </c>
+      <c r="G12" s="5" t="s">
         <v>38</v>
-      </c>
-      <c r="D12" t="s">
-        <v>54</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="F12" s="4">
-        <v>39492</v>
-      </c>
-      <c r="G12" s="5" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
+        <v>20</v>
+      </c>
+      <c r="B13" t="s">
         <v>19</v>
       </c>
-      <c r="B13" t="s">
-        <v>20</v>
-      </c>
       <c r="C13" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D13" t="s">
-        <v>57</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>78</v>
-      </c>
+        <v>53</v>
+      </c>
+      <c r="E13" s="1"/>
       <c r="F13" s="4">
-        <v>39724</v>
+        <v>39826</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -1691,20 +1680,22 @@
         <v>21</v>
       </c>
       <c r="B14" t="s">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="C14" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D14" t="s">
-        <v>55</v>
-      </c>
-      <c r="E14" s="1"/>
+        <v>54</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>76</v>
+      </c>
       <c r="F14" s="4">
-        <v>39826</v>
+        <v>39660</v>
       </c>
       <c r="G14" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -1712,22 +1703,22 @@
         <v>22</v>
       </c>
       <c r="B15" t="s">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="C15" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D15" t="s">
-        <v>56</v>
+        <v>96</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="F15" s="4">
-        <v>39660</v>
+        <v>39463</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -1735,22 +1726,22 @@
         <v>23</v>
       </c>
       <c r="B16" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="C16" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D16" t="s">
-        <v>99</v>
+        <v>56</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F16" s="4">
-        <v>39463</v>
+        <v>39507</v>
       </c>
       <c r="G16" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -1758,22 +1749,22 @@
         <v>24</v>
       </c>
       <c r="B17" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C17" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D17" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="F17" s="4">
-        <v>39507</v>
+        <v>39547</v>
       </c>
       <c r="G17" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -1781,22 +1772,22 @@
         <v>25</v>
       </c>
       <c r="B18" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="C18" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D18" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="F18" s="4">
-        <v>39547</v>
+        <v>39644</v>
       </c>
       <c r="G18" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -1804,22 +1795,22 @@
         <v>26</v>
       </c>
       <c r="B19" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="C19" t="s">
         <v>36</v>
       </c>
       <c r="D19" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>96</v>
+        <v>80</v>
       </c>
       <c r="F19" s="4">
-        <v>39644</v>
+        <v>39992</v>
       </c>
       <c r="G19" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -1830,19 +1821,19 @@
         <v>8</v>
       </c>
       <c r="C20" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D20" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="F20" s="4">
-        <v>39992</v>
+        <v>39582</v>
       </c>
       <c r="G20" s="5" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
     </row>
     <row r="21" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -1850,22 +1841,22 @@
         <v>28</v>
       </c>
       <c r="B21" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="C21" t="s">
         <v>36</v>
       </c>
       <c r="D21" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="F21" s="4">
-        <v>39582</v>
+        <v>39682</v>
       </c>
       <c r="G21" s="5" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="22" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -1873,22 +1864,22 @@
         <v>29</v>
       </c>
       <c r="B22" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C22" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D22" t="s">
-        <v>63</v>
+        <v>90</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="F22" s="4">
-        <v>39682</v>
+        <v>39468</v>
       </c>
       <c r="G22" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="23" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -1896,22 +1887,22 @@
         <v>30</v>
       </c>
       <c r="B23" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C23" t="s">
         <v>37</v>
       </c>
       <c r="D23" t="s">
-        <v>93</v>
+        <v>62</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="F23" s="4">
-        <v>39468</v>
+        <v>39783</v>
       </c>
       <c r="G23" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="24" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -1919,22 +1910,22 @@
         <v>31</v>
       </c>
       <c r="B24" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="C24" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="D24" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="F24" s="4">
-        <v>39783</v>
+        <v>39458</v>
       </c>
       <c r="G24" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="25" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -1942,22 +1933,22 @@
         <v>32</v>
       </c>
       <c r="B25" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="C25" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D25" t="s">
+        <v>64</v>
+      </c>
+      <c r="E25" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="E25" s="1" t="s">
-        <v>87</v>
-      </c>
       <c r="F25" s="4">
-        <v>39458</v>
+        <v>39753</v>
       </c>
       <c r="G25" s="5" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
     </row>
     <row r="26" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -1965,95 +1956,72 @@
         <v>33</v>
       </c>
       <c r="B26" t="s">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="C26" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D26" t="s">
-        <v>66</v>
+        <v>97</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="F26" s="4">
+        <v>98</v>
+      </c>
+      <c r="F26" s="6">
         <v>39753</v>
       </c>
-      <c r="G26" s="5" t="s">
-        <v>39</v>
+      <c r="G26" s="8" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="27" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="B27" t="s">
+        <v>12</v>
+      </c>
+      <c r="C27" t="s">
+        <v>37</v>
+      </c>
+      <c r="D27" t="s">
+        <v>91</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="F27" s="7"/>
+      <c r="G27" s="9"/>
+    </row>
+    <row r="28" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="B28" t="s">
         <v>3</v>
       </c>
-      <c r="C27" t="s">
+      <c r="C28" t="s">
         <v>36</v>
       </c>
-      <c r="D27" t="s">
-        <v>100</v>
-      </c>
-      <c r="E27" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="F27" s="6">
-        <v>39753</v>
-      </c>
-      <c r="G27" s="8" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A28" t="s">
-        <v>40</v>
-      </c>
-      <c r="B28" t="s">
-        <v>12</v>
-      </c>
-      <c r="C28" t="s">
-        <v>38</v>
-      </c>
       <c r="D28" t="s">
-        <v>94</v>
-      </c>
-      <c r="E28" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="E28" s="12" t="s">
         <v>88</v>
       </c>
-      <c r="F28" s="7"/>
-      <c r="G28" s="9"/>
-    </row>
-    <row r="29" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="10" t="s">
-        <v>89</v>
-      </c>
-      <c r="B29" t="s">
-        <v>3</v>
-      </c>
-      <c r="C29" t="s">
-        <v>37</v>
-      </c>
-      <c r="D29" t="s">
-        <v>90</v>
-      </c>
-      <c r="E29" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="F29" s="11">
+      <c r="F28" s="11">
         <v>39517</v>
       </c>
-      <c r="G29" s="5" t="s">
-        <v>42</v>
+      <c r="G28" s="5" t="s">
+        <v>41</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="19" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="E3" r:id="rId1" xr:uid="{793807AE-2254-408E-97A4-C80ACB7D2E05}"/>
-    <hyperlink ref="E29" r:id="rId2" xr:uid="{2903A663-6F05-4D95-887A-983FD2DF64E6}"/>
-    <hyperlink ref="E19" r:id="rId3" xr:uid="{4376FC9B-16F2-4F4B-89D6-FE200E74D3BC}"/>
+    <hyperlink ref="E28" r:id="rId2" xr:uid="{2903A663-6F05-4D95-887A-983FD2DF64E6}"/>
+    <hyperlink ref="E18" r:id="rId3" xr:uid="{4376FC9B-16F2-4F4B-89D6-FE200E74D3BC}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
